--- a/data/vendor-search/results_all_streaming.xlsx
+++ b/data/vendor-search/results_all_streaming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,8 +477,10 @@
       <c r="D2" t="n">
         <v>7.8</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -483,6 +490,11 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>cpe:2.3:h:sony:bravia_tv:kdl-32cx525:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>sony bravia</t>
         </is>
       </c>
     </row>
@@ -505,8 +517,10 @@
       <c r="D3" t="n">
         <v>5.4</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -516,6 +530,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:itunes:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -538,8 +557,10 @@
       <c r="D4" t="n">
         <v>2.1</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,6 +570,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:7.0.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -571,8 +597,10 @@
       <c r="D5" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -582,6 +610,11 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:8.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:8.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:8.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.10.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:7.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -604,8 +637,10 @@
       <c r="D6" t="n">
         <v>5.8</v>
       </c>
-      <c r="E6" t="n">
-        <v>2</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -615,6 +650,11 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:8.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:8.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:8.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:7.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -637,8 +677,10 @@
       <c r="D7" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E7" t="n">
-        <v>3</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -648,6 +690,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>cpe:2.3:o:openelec:openelec:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>openelec</t>
         </is>
       </c>
     </row>
@@ -670,8 +717,10 @@
       <c r="D8" t="n">
         <v>7.5</v>
       </c>
-      <c r="E8" t="n">
-        <v>3</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -681,6 +730,11 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>cpe:2.3:h:allwinner:a64:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:athlon_ii_640_x4:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:e-350:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:fx-8120_8-core:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:fx-8320_8-core:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:fx-8350_8-core:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:phenom_9550_4-core:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:atom_c2750:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:celeron_n2840:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i5_m480:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-2620qm:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-3632qm:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-4500u:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-6700k:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7_920:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:xeon_e3-1240_v5:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:xeon_e5-2658_v2:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:tegra_k1_cd570m-a1:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:tegra_k1_cd580m-a1:-:*:*:*:*:*:*:*|cpe:2.3:h:samsung:exynos_5800:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>allwinner</t>
         </is>
       </c>
     </row>
@@ -703,8 +757,10 @@
       <c r="D9" t="n">
         <v>7.5</v>
       </c>
-      <c r="E9" t="n">
-        <v>3</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -714,6 +770,11 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>cpe:2.3:h:allwinner:a64:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:athlon_ii_640_x4:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:e-350:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:fx-8120_8-core:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:fx-8320_8-core:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:fx-8350_8-core:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:phenom_9550_4-core:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:atom_c2750:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:celeron_n2840:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i5_m480:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-2620qm:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-3632qm:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-4500u:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-6700k:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7_920:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:xeon_e3-1240_v5:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:xeon_e5-2658_v2:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:tegra_k1_cd570m-a1:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:tegra_k1_cd580m-a1:-:*:*:*:*:*:*:*|cpe:2.3:h:samsung:exynos_5800:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>allwinner</t>
         </is>
       </c>
     </row>
@@ -736,8 +797,10 @@
       <c r="D10" t="n">
         <v>7.5</v>
       </c>
-      <c r="E10" t="n">
-        <v>3</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -747,6 +810,11 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>cpe:2.3:h:allwinner:a64:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:athlon_ii_640_x4:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:e-350:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:fx-8120_8-core:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:fx-8320_8-core:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:fx-8350_8-core:-:*:*:*:*:*:*:*|cpe:2.3:h:amd:phenom_9550_4-core:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:atom_c2750:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:celeron_n2840:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i5_m480:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-2620qm:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-3632qm:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-4500u:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7-6700k:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:core_i7_920:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:xeon_e3-1240_v5:-:*:*:*:*:*:*:*|cpe:2.3:h:intel:xeon_e5-2658_v2:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:tegra_k1_cd570m-a1:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:tegra_k1_cd580m-a1:-:*:*:*:*:*:*:*|cpe:2.3:h:samsung:exynos_5800:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>allwinner</t>
         </is>
       </c>
     </row>
@@ -769,8 +837,10 @@
       <c r="D11" t="n">
         <v>7.5</v>
       </c>
-      <c r="E11" t="n">
-        <v>3</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -780,6 +850,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>cpe:2.3:a:kodi:kodi:17.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>kodi</t>
         </is>
       </c>
     </row>
@@ -802,8 +877,10 @@
       <c r="D12" t="n">
         <v>8.1</v>
       </c>
-      <c r="E12" t="n">
-        <v>3</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -813,6 +890,11 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>cpe:2.3:o:openelec:openelec:6.0.3:*:*:*:*:*:*:*|cpe:2.3:o:openelec:openelec:7.0.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>openelec</t>
         </is>
       </c>
     </row>
@@ -835,8 +917,10 @@
       <c r="D13" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E13" t="n">
-        <v>3</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -846,6 +930,11 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>cpe:2.3:o:samsung:nt14u_firmware:t-nt14uakucb-1008.0:*:*:*:*:*:*:*|cpe:2.3:h:samsung:nt14u_us:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x14j_firmware:t-ms14jakucb-1102.5:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x14j_us:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x14h_firmware:t-mst14dcncb-1010.0:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x14h_cn:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x12_firmware:t-mst12akucb-1114.0:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x12_us:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x10p_firmware:t-mst10pibrcb-1104.0:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x10p_ibr:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:nt14u_firmware:t-nt14udeucb-1007.1:*:*:*:*:*:*:*|cpe:2.3:h:samsung:nt14u_eu:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:nt14u_firmware:t-nt14udcncb-1003.1:*:*:*:*:*:*:*|cpe:2.3:h:samsung:nt14u_cn:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x14j_firmware:t-ms14jdeucb-1018.0:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x14j_eu:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x14j_firmware:t-ms14jdcncb-1004.2:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x14j_cn:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x14h_firmware:t-mst14akucb-1100.4:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x14h_us:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x14h_firmware:t-mst14deucb-1023.0:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x14h_eu:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x12_firmware:t-mst12deucb-1111.4:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x12_eu:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x10p_firmware:t-mst10pauscp-1302.0:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x10p_us:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:x10p_firmware:t-mst10pdeucb-1210.0:*:*:*:*:*:*:*|cpe:2.3:h:samsung:x10p_eu:-:*:*:*:*:*:*:*|cpe:2.3:o:samsung:m288ofw_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:samsung:m288ofw:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>samsung smart tv</t>
         </is>
       </c>
     </row>
@@ -868,8 +957,10 @@
       <c r="D14" t="n">
         <v>7.8</v>
       </c>
-      <c r="E14" t="n">
-        <v>3.1</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -879,6 +970,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>cpe:2.3:o:allwinner:linux-3.4-sunxi:-:*:*:*:*:*:*:*|cpe:2.3:h:allwinner:a83t:-:*:*:*:*:*:*:*|cpe:2.3:h:allwinner:h3:-:*:*:*:*:*:*:*|cpe:2.3:h:allwinner:h8:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>allwinner</t>
         </is>
       </c>
     </row>
@@ -901,8 +997,10 @@
       <c r="D15" t="n">
         <v>7.5</v>
       </c>
-      <c r="E15" t="n">
-        <v>3</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -912,6 +1010,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>cpe:2.3:o:cisco:yesmax_hd_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:cisco:yesmax_hd:-:*:*:*:*:*:*:*|cpe:2.3:o:cisco:yesmaxtotal_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:cisco:yesmaxtotal:-:*:*:*:*:*:*:*|cpe:2.3:o:cisco:yesquattro_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:cisco:yesquattro:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>set-top box</t>
         </is>
       </c>
     </row>
@@ -934,8 +1037,10 @@
       <c r="D16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E16" t="n">
-        <v>3</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -945,6 +1050,11 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>cpe:2.3:a:openwebif_project:openwebif:1.2.5:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>set-top box</t>
         </is>
       </c>
     </row>
@@ -967,8 +1077,10 @@
       <c r="D17" t="n">
         <v>9.6</v>
       </c>
-      <c r="E17" t="n">
-        <v>3</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -978,6 +1090,11 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>cpe:2.3:h:roku:roku_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:roku:roku:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>roku</t>
         </is>
       </c>
     </row>
@@ -1000,8 +1117,10 @@
       <c r="D18" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E18" t="n">
-        <v>3</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1011,6 +1130,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sony:r5c_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32r500c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32r503c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32r505c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40r550c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40r553c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40r555c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48r550c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48r553c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48r555c:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:wd75_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd751:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd752:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd756:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd757:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd758:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd759:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd751:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd752:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd756:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd757:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd758:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd759:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd751:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd752:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd756:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd757:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd758:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd759:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:wd65_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40wd650:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40wd653:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40wd655:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48wd650:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48wd653:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48wd655:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:xe70_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7000:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7073:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7077:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7096:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7000:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7073:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7077:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7096:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7000:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7073:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7077:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7096:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7096:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:xf70_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:xf70:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:we75_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we755:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:we6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32we610:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32we613:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32we615:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40we660:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40we663:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40we665:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we660:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we663:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we665:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:wf6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:wf6:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>sony bravia</t>
         </is>
       </c>
     </row>
@@ -1033,8 +1157,10 @@
       <c r="D19" t="n">
         <v>8.1</v>
       </c>
-      <c r="E19" t="n">
-        <v>3</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1044,6 +1170,11 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sony:r5c_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32r500c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32r503c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32r505c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40r550c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40r553c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40r555c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48r550c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48r553c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48r555c:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:wd75_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd751:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd752:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd756:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd757:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd758:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd759:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd751:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd752:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd756:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd757:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd758:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd759:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd751:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd752:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd756:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd757:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd758:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd759:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:wd65_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40wd650:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40wd653:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40wd655:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48wd650:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48wd653:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48wd655:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:xe70_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7000:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7073:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7077:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7096:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7000:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7073:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7077:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7096:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7000:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7073:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7077:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7096:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7096:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:xf70_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:xf70:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:we75_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we755:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:we6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32we610:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32we613:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32we615:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40we660:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40we663:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40we665:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we660:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we663:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we665:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:wf6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:wf6:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>sony bravia</t>
         </is>
       </c>
     </row>
@@ -1066,8 +1197,10 @@
       <c r="D20" t="n">
         <v>6.5</v>
       </c>
-      <c r="E20" t="n">
-        <v>3</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1077,6 +1210,11 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sony:r5c_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32r500c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32r503c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32r505c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40r550c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40r553c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40r555c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48r550c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48r553c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48r555c:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:wd75_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd751:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd752:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd756:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd757:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd758:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32wd759:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd751:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd752:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd756:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd757:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd758:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43wd759:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd751:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd752:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd756:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd757:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd758:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49wd759:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:wd65_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40wd650:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40wd653:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40wd655:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48wd650:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48wd653:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-48wd655:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:xe70_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7000:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7073:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7077:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-43xe7096:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7000:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7073:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7077:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-49xe7096:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7000:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7073:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7077:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-55xe7096:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7002:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7003:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7004:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7005:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7093:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kd-65xe7096:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:xf70_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:xf70:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:we75_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-43we755:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we750:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we753:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we754:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we755:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:we6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32we610:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32we613:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-32we615:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40we660:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40we663:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-40we665:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we660:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we663:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-49we665:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:wf6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:wf6:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>sony bravia</t>
         </is>
       </c>
     </row>
@@ -1099,8 +1237,10 @@
       <c r="D21" t="n">
         <v>7.5</v>
       </c>
-      <c r="E21" t="n">
-        <v>3</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -1108,6 +1248,11 @@
           <t>cpe:2.3:o:sony:bravia_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:bravia:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>sony bravia</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1128,8 +1273,10 @@
       <c r="D22" t="n">
         <v>7.5</v>
       </c>
-      <c r="E22" t="n">
-        <v>3</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1139,6 +1286,11 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sony:bravia_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:bravia:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>sony bravia</t>
         </is>
       </c>
     </row>
@@ -1161,8 +1313,10 @@
       <c r="D23" t="n">
         <v>7.8</v>
       </c>
-      <c r="E23" t="n">
-        <v>3</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1172,6 +1326,11 @@
       <c r="G23" t="inlineStr">
         <is>
           <t>cpe:2.3:a:nvidia:shield_experience:*:*:*:*:*:*:*:*|cpe:2.3:o:google:android:8.0:*:*:*:*:*:*:*|cpe:2.3:o:google:android:8.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>nvidia shield</t>
         </is>
       </c>
     </row>
@@ -1194,8 +1353,10 @@
       <c r="D24" t="n">
         <v>7.8</v>
       </c>
-      <c r="E24" t="n">
-        <v>3</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -1203,6 +1364,11 @@
           <t>cpe:2.3:a:nvidia:shield_experience:*:*:*:*:*:*:*:*|cpe:2.3:o:google:android:8.0:*:*:*:*:*:*:*|cpe:2.3:o:google:android:8.1:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>nvidia shield</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,8 +1389,10 @@
       <c r="D25" t="n">
         <v>7.8</v>
       </c>
-      <c r="E25" t="n">
-        <v>3</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -1232,6 +1400,11 @@
           <t>cpe:2.3:a:nvidia:shield_experience:*:*:*:*:*:*:*:*|cpe:2.3:o:google:android:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>nvidia shield</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1252,8 +1425,10 @@
       <c r="D26" t="n">
         <v>4.3</v>
       </c>
-      <c r="E26" t="n">
-        <v>3.1</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -1261,6 +1436,11 @@
           <t>cpe:2.3:o:apple:apple_tv:*:*:*:*:*:fire_os:*:*</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1281,8 +1461,10 @@
       <c r="D27" t="n">
         <v>5.3</v>
       </c>
-      <c r="E27" t="n">
-        <v>3.1</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1292,6 +1474,11 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>cpe:2.3:o:virginmedia:super_hub_3_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:virginmedia:super_hub_3:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>virgin media</t>
         </is>
       </c>
     </row>
@@ -1314,8 +1501,10 @@
       <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E28" t="n">
-        <v>3.1</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -1323,6 +1512,11 @@
           <t>cpe:2.3:o:skyworth:penguin_aurora_box_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:skyworth:penguin_aurora_box:41502:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>set-top box</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1343,8 +1537,10 @@
       <c r="D29" t="n">
         <v>5.5</v>
       </c>
-      <c r="E29" t="n">
-        <v>3.1</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1354,6 +1550,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>cpe:2.3:a:kodi:kodi:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>kodi</t>
         </is>
       </c>
     </row>
@@ -1376,8 +1577,10 @@
       <c r="D30" t="n">
         <v>7.5</v>
       </c>
-      <c r="E30" t="n">
-        <v>3.1</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1387,6 +1590,11 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>cpe:2.3:a:siemens:siveillance_video_management_software_2019_r1:*:*:*:*:*:*:*:*|cpe:2.3:a:siemens:siveillance_video_management_software_2019_r2:*:*:*:*:*:*:*:*|cpe:2.3:a:siemens:siveillance_video_management_software_2019_r3:*:*:*:*:*:*:*:*|cpe:2.3:a:siemens:siveillance_video_management_software_2020_r1:-:*:*:*:*:*:*:*|cpe:2.3:a:siemens:siveillance_video_management_software_2020_r2:-:*:*:*:*:*:*:*|cpe:2.3:h:siemens:siveillance_video_dlna_server:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>dlna</t>
         </is>
       </c>
     </row>
@@ -1409,8 +1617,10 @@
       <c r="D31" t="n">
         <v>5.7</v>
       </c>
-      <c r="E31" t="n">
-        <v>3.1</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -1418,6 +1628,11 @@
           <t>cpe:2.3:o:roku:roku_os:*:*:*:*:*:*:*:*|cpe:2.3:h:roku:express:-:*:*:*:*:*:*:*|cpe:2.3:h:roku:express_4k\+:-:*:*:*:*:*:*:*|cpe:2.3:h:roku:roku_tv:-:*:*:*:*:*:*:*|cpe:2.3:h:roku:streambar:-:*:*:*:*:*:*:*|cpe:2.3:h:roku:streambar_pro:-:*:*:*:*:*:*:*|cpe:2.3:h:roku:streaming_stick_4k:-:*:*:*:*:*:*:*|cpe:2.3:h:roku:streaming_stick_4k\+:-:*:*:*:*:*:*:*|cpe:2.3:h:roku:ultra:-:*:*:*:*:*:*:*|cpe:2.3:h:roku:wireless_speakers:-:*:*:*:*:*:*:*|cpe:2.3:h:roku:wireless_subwoofer:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>roku</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1438,8 +1653,10 @@
       <c r="D32" t="n">
         <v>3.3</v>
       </c>
-      <c r="E32" t="n">
-        <v>3.1</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1449,6 +1666,11 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>cpe:2.3:o:google:android:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>dlna</t>
         </is>
       </c>
     </row>
@@ -1471,8 +1693,10 @@
       <c r="D33" t="n">
         <v>4.6</v>
       </c>
-      <c r="E33" t="n">
-        <v>3.1</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1482,6 +1706,11 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>cpe:2.3:a:kodi:kodi:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>kodi</t>
         </is>
       </c>
     </row>
@@ -1504,8 +1733,10 @@
       <c r="D34" t="n">
         <v>4.3</v>
       </c>
-      <c r="E34" t="n">
-        <v>3.1</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1515,6 +1746,11 @@
       <c r="G34" t="inlineStr">
         <is>
           <t>cpe:2.3:o:samsung:ue40d7000_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:samsung:ue40d7000:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>samsung smart tv</t>
         </is>
       </c>
     </row>
@@ -1537,8 +1773,10 @@
       <c r="D35" t="n">
         <v>5.5</v>
       </c>
-      <c r="E35" t="n">
-        <v>3.1</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1548,6 +1786,11 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:apple_tv:*:*:*:*:*:windows:*:*|cpe:2.3:a:apple:itunes:*:*:*:*:*:windows:*:*</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -1570,8 +1813,10 @@
       <c r="D36" t="n">
         <v>6.8</v>
       </c>
-      <c r="E36" t="n">
-        <v>2</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1581,6 +1826,11 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>cpe:2.3:a:openelec:openelec:*:*:*:*:*:*:*:*|cpe:2.3:a:openelec:openelec:2.02:*:*:*:*:*:*:*|cpe:2.3:a:openelec:openelec:3.00:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>openelec</t>
         </is>
       </c>
     </row>
@@ -1603,8 +1853,10 @@
       <c r="D37" t="n">
         <v>7.8</v>
       </c>
-      <c r="E37" t="n">
-        <v>2</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1614,6 +1866,11 @@
       <c r="G37" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:apple_tv:4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.1.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -1636,8 +1893,10 @@
       <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E38" t="n">
-        <v>2</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1647,6 +1906,11 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:apple_tv:4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.1.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -1669,8 +1933,10 @@
       <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E39" t="n">
-        <v>2</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1680,6 +1946,11 @@
       <c r="G39" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:apple_tv:4.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:apple_tv:4.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:apple_tv:4.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:apple_tv:4.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.2:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.3:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.8:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:-:ipodtouch:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -1702,8 +1973,10 @@
       <c r="D40" t="n">
         <v>2.6</v>
       </c>
-      <c r="E40" t="n">
-        <v>2</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1713,6 +1986,11 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:apple_tv:4.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:apple_tv:4.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:apple_tv:4.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:apple_tv:4.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.2:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.3:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:-:iphone:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.8:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:-:ipodtouch:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -1735,8 +2013,10 @@
       <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E41" t="n">
-        <v>2</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
@@ -1744,6 +2024,11 @@
           <t>cpe:2.3:o:sharp:aquos_hn-pp150_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_hn-pp150:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>sharp aquos</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1764,8 +2049,10 @@
       <c r="D42" t="n">
         <v>3.6</v>
       </c>
-      <c r="E42" t="n">
-        <v>2</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1775,6 +2062,11 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -1797,8 +2089,10 @@
       <c r="D43" t="n">
         <v>4.6</v>
       </c>
-      <c r="E43" t="n">
-        <v>2</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -1806,6 +2100,11 @@
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.3:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.4:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.5:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.3:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.8:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0.1:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.1.1:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1826,8 +2125,10 @@
       <c r="D44" t="n">
         <v>2.1</v>
       </c>
-      <c r="E44" t="n">
-        <v>2</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1837,6 +2138,11 @@
       <c r="G44" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.3:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.4:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.5:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.3:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.8:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0.1:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.1.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -1859,8 +2165,10 @@
       <c r="D45" t="n">
         <v>7.2</v>
       </c>
-      <c r="E45" t="n">
-        <v>2</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -1868,6 +2176,11 @@
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.3:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.4:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:1.1.5:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.0.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:2.2.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.1.3:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.1:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:3.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.2.8:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:4.3.5:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0.1:-:ipad:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.0.1:-:ipodtouch:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:5.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:1.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.3.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:2.4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:3.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.2.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.3.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:4.4.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.1.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:5.1.1:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1888,8 +2201,10 @@
       <c r="D46" t="n">
         <v>7.4</v>
       </c>
-      <c r="E46" t="n">
-        <v>3.1</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1899,6 +2214,11 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -1921,8 +2241,10 @@
       <c r="D47" t="n">
         <v>5.8</v>
       </c>
-      <c r="E47" t="n">
-        <v>2</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1932,6 +2254,11 @@
       <c r="G47" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -1954,8 +2281,10 @@
       <c r="D48" t="n">
         <v>7.8</v>
       </c>
-      <c r="E48" t="n">
-        <v>2</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1965,6 +2294,11 @@
       <c r="G48" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -1987,8 +2321,10 @@
       <c r="D49" t="n">
         <v>6.3</v>
       </c>
-      <c r="E49" t="n">
-        <v>2</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1998,6 +2334,11 @@
       <c r="G49" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2020,8 +2361,10 @@
       <c r="D50" t="n">
         <v>5.8</v>
       </c>
-      <c r="E50" t="n">
-        <v>2</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2031,6 +2374,11 @@
       <c r="G50" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2053,8 +2401,10 @@
       <c r="D51" t="n">
         <v>6.8</v>
       </c>
-      <c r="E51" t="n">
-        <v>2</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2064,6 +2414,11 @@
       <c r="G51" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2086,8 +2441,10 @@
       <c r="D52" t="n">
         <v>7.2</v>
       </c>
-      <c r="E52" t="n">
-        <v>2</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2097,6 +2454,11 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2119,8 +2481,10 @@
       <c r="D53" t="n">
         <v>2.1</v>
       </c>
-      <c r="E53" t="n">
-        <v>2</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2130,6 +2494,11 @@
       <c r="G53" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2152,8 +2521,10 @@
       <c r="D54" t="n">
         <v>7.1</v>
       </c>
-      <c r="E54" t="n">
-        <v>2</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -2161,6 +2532,11 @@
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2181,8 +2557,10 @@
       <c r="D55" t="n">
         <v>5.8</v>
       </c>
-      <c r="E55" t="n">
-        <v>2</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2192,6 +2570,11 @@
       <c r="G55" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2214,8 +2597,10 @@
       <c r="D56" t="n">
         <v>7.2</v>
       </c>
-      <c r="E56" t="n">
-        <v>2</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2225,6 +2610,11 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2247,8 +2637,10 @@
       <c r="D57" t="n">
         <v>6.8</v>
       </c>
-      <c r="E57" t="n">
-        <v>2</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2258,6 +2650,11 @@
       <c r="G57" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2280,8 +2677,10 @@
       <c r="D58" t="n">
         <v>6.8</v>
       </c>
-      <c r="E58" t="n">
-        <v>2</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2291,6 +2690,11 @@
       <c r="G58" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2313,8 +2717,10 @@
       <c r="D59" t="n">
         <v>6.8</v>
       </c>
-      <c r="E59" t="n">
-        <v>2</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2324,6 +2730,11 @@
       <c r="G59" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2346,8 +2757,10 @@
       <c r="D60" t="n">
         <v>6.8</v>
       </c>
-      <c r="E60" t="n">
-        <v>2</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2357,6 +2770,11 @@
       <c r="G60" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2379,8 +2797,10 @@
       <c r="D61" t="n">
         <v>6.8</v>
       </c>
-      <c r="E61" t="n">
-        <v>2</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2390,6 +2810,11 @@
       <c r="G61" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2412,8 +2837,10 @@
       <c r="D62" t="n">
         <v>6.8</v>
       </c>
-      <c r="E62" t="n">
-        <v>2</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2423,6 +2850,11 @@
       <c r="G62" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2445,8 +2877,10 @@
       <c r="D63" t="n">
         <v>6.8</v>
       </c>
-      <c r="E63" t="n">
-        <v>2</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2456,6 +2890,11 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.5:supplemental_update:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2478,8 +2917,10 @@
       <c r="D64" t="n">
         <v>4.3</v>
       </c>
-      <c r="E64" t="n">
-        <v>2</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2489,6 +2930,11 @@
       <c r="G64" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.8.5:supplemental_update:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.7.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.7.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.7.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.7.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x_server:10.7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x_server:10.7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x_server:10.7.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x_server:10.7.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x_server:10.7.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x_server:10.7.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2511,8 +2957,10 @@
       <c r="D65" t="n">
         <v>4.9</v>
       </c>
-      <c r="E65" t="n">
-        <v>2</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2522,6 +2970,11 @@
       <c r="G65" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2544,8 +2997,10 @@
       <c r="D66" t="n">
         <v>6.8</v>
       </c>
-      <c r="E66" t="n">
-        <v>2</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2555,6 +3010,11 @@
       <c r="G66" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.3:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2577,8 +3037,10 @@
       <c r="D67" t="n">
         <v>4.9</v>
       </c>
-      <c r="E67" t="n">
-        <v>2</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
@@ -2586,6 +3048,11 @@
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2606,8 +3073,10 @@
       <c r="D68" t="n">
         <v>10</v>
       </c>
-      <c r="E68" t="n">
-        <v>2</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2617,6 +3086,11 @@
       <c r="G68" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:10.9:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2639,8 +3113,10 @@
       <c r="D69" t="n">
         <v>10</v>
       </c>
-      <c r="E69" t="n">
-        <v>2</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2650,6 +3126,11 @@
       <c r="G69" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.3:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2672,8 +3153,10 @@
       <c r="D70" t="n">
         <v>10</v>
       </c>
-      <c r="E70" t="n">
-        <v>2</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2683,6 +3166,11 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:10.9:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2705,8 +3193,10 @@
       <c r="D71" t="n">
         <v>10</v>
       </c>
-      <c r="E71" t="n">
-        <v>2</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2716,6 +3206,11 @@
       <c r="G71" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.3:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2738,8 +3233,10 @@
       <c r="D72" t="n">
         <v>5</v>
       </c>
-      <c r="E72" t="n">
-        <v>2</v>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2749,6 +3246,11 @@
       <c r="G72" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:10.9:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:10.9.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2771,8 +3273,10 @@
       <c r="D73" t="n">
         <v>6.8</v>
       </c>
-      <c r="E73" t="n">
-        <v>2</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2782,6 +3286,11 @@
       <c r="G73" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.3:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2804,8 +3313,10 @@
       <c r="D74" t="n">
         <v>6.8</v>
       </c>
-      <c r="E74" t="n">
-        <v>2</v>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2815,6 +3326,11 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2837,8 +3353,10 @@
       <c r="D75" t="n">
         <v>6.8</v>
       </c>
-      <c r="E75" t="n">
-        <v>2</v>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2848,6 +3366,11 @@
       <c r="G75" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2870,8 +3393,10 @@
       <c r="D76" t="n">
         <v>6.8</v>
       </c>
-      <c r="E76" t="n">
-        <v>2</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2881,6 +3406,11 @@
       <c r="G76" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.3:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2903,8 +3433,10 @@
       <c r="D77" t="n">
         <v>6.8</v>
       </c>
-      <c r="E77" t="n">
-        <v>2</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2914,6 +3446,11 @@
       <c r="G77" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.3:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2936,8 +3473,10 @@
       <c r="D78" t="n">
         <v>6.8</v>
       </c>
-      <c r="E78" t="n">
-        <v>2</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2947,6 +3486,11 @@
       <c r="G78" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -2969,8 +3513,10 @@
       <c r="D79" t="n">
         <v>6.8</v>
       </c>
-      <c r="E79" t="n">
-        <v>2</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2980,6 +3526,11 @@
       <c r="G79" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.3:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3002,8 +3553,10 @@
       <c r="D80" t="n">
         <v>6.8</v>
       </c>
-      <c r="E80" t="n">
-        <v>2</v>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3013,6 +3566,11 @@
       <c r="G80" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:6.1.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3035,8 +3593,10 @@
       <c r="D81" t="n">
         <v>5.5</v>
       </c>
-      <c r="E81" t="n">
-        <v>2</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3046,6 +3606,11 @@
       <c r="G81" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3068,8 +3633,10 @@
       <c r="D82" t="n">
         <v>2.1</v>
       </c>
-      <c r="E82" t="n">
-        <v>2</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3079,6 +3646,11 @@
       <c r="G82" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3101,8 +3673,10 @@
       <c r="D83" t="n">
         <v>5.6</v>
       </c>
-      <c r="E83" t="n">
-        <v>3</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3112,6 +3686,11 @@
       <c r="G83" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3134,8 +3713,10 @@
       <c r="D84" t="n">
         <v>7.8</v>
       </c>
-      <c r="E84" t="n">
-        <v>2</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
@@ -3143,6 +3724,11 @@
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3163,8 +3749,10 @@
       <c r="D85" t="n">
         <v>1.9</v>
       </c>
-      <c r="E85" t="n">
-        <v>2</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3174,6 +3762,11 @@
       <c r="G85" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3196,8 +3789,10 @@
       <c r="D86" t="n">
         <v>3.6</v>
       </c>
-      <c r="E86" t="n">
-        <v>2</v>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3207,6 +3802,11 @@
       <c r="G86" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3229,8 +3829,10 @@
       <c r="D87" t="n">
         <v>5.5</v>
       </c>
-      <c r="E87" t="n">
-        <v>3</v>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
@@ -3238,6 +3840,11 @@
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3258,8 +3865,10 @@
       <c r="D88" t="n">
         <v>7.8</v>
       </c>
-      <c r="E88" t="n">
-        <v>3</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
@@ -3267,6 +3876,11 @@
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3287,8 +3901,10 @@
       <c r="D89" t="n">
         <v>6.8</v>
       </c>
-      <c r="E89" t="n">
-        <v>2</v>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3298,6 +3914,11 @@
       <c r="G89" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3320,8 +3941,10 @@
       <c r="D90" t="n">
         <v>5.8</v>
       </c>
-      <c r="E90" t="n">
-        <v>2</v>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3331,6 +3954,11 @@
       <c r="G90" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3353,8 +3981,10 @@
       <c r="D91" t="n">
         <v>7.1</v>
       </c>
-      <c r="E91" t="n">
-        <v>2</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3364,6 +3994,11 @@
       <c r="G91" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3386,8 +4021,10 @@
       <c r="D92" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E92" t="n">
-        <v>2</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3397,6 +4034,11 @@
       <c r="G92" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3419,8 +4061,10 @@
       <c r="D93" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E93" t="n">
-        <v>2</v>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3430,6 +4074,11 @@
       <c r="G93" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3452,8 +4101,10 @@
       <c r="D94" t="n">
         <v>4.3</v>
       </c>
-      <c r="E94" t="n">
-        <v>2</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3463,6 +4114,11 @@
       <c r="G94" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3485,8 +4141,10 @@
       <c r="D95" t="n">
         <v>7.8</v>
       </c>
-      <c r="E95" t="n">
-        <v>3</v>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3496,6 +4154,11 @@
       <c r="G95" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3518,8 +4181,10 @@
       <c r="D96" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E96" t="n">
-        <v>2</v>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3529,6 +4194,11 @@
       <c r="G96" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3551,8 +4221,10 @@
       <c r="D97" t="n">
         <v>7.8</v>
       </c>
-      <c r="E97" t="n">
-        <v>3.1</v>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3562,6 +4234,11 @@
       <c r="G97" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3584,8 +4261,10 @@
       <c r="D98" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E98" t="n">
-        <v>2</v>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
@@ -3593,6 +4272,11 @@
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3613,8 +4297,10 @@
       <c r="D99" t="n">
         <v>3.3</v>
       </c>
-      <c r="E99" t="n">
-        <v>3</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3624,6 +4310,11 @@
       <c r="G99" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3646,8 +4337,10 @@
       <c r="D100" t="n">
         <v>6.9</v>
       </c>
-      <c r="E100" t="n">
-        <v>2</v>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3657,6 +4350,11 @@
       <c r="G100" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3679,8 +4377,10 @@
       <c r="D101" t="n">
         <v>6.8</v>
       </c>
-      <c r="E101" t="n">
-        <v>2</v>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3690,6 +4390,11 @@
       <c r="G101" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3712,8 +4417,10 @@
       <c r="D102" t="n">
         <v>6.8</v>
       </c>
-      <c r="E102" t="n">
-        <v>2</v>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3723,6 +4430,11 @@
       <c r="G102" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3745,8 +4457,10 @@
       <c r="D103" t="n">
         <v>6.8</v>
       </c>
-      <c r="E103" t="n">
-        <v>2</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3756,6 +4470,11 @@
       <c r="G103" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3778,8 +4497,10 @@
       <c r="D104" t="n">
         <v>6.8</v>
       </c>
-      <c r="E104" t="n">
-        <v>2</v>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3789,6 +4510,11 @@
       <c r="G104" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3811,8 +4537,10 @@
       <c r="D105" t="n">
         <v>6.8</v>
       </c>
-      <c r="E105" t="n">
-        <v>2</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3822,6 +4550,11 @@
       <c r="G105" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3844,8 +4577,10 @@
       <c r="D106" t="n">
         <v>6.8</v>
       </c>
-      <c r="E106" t="n">
-        <v>2</v>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3855,6 +4590,11 @@
       <c r="G106" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:safari:6.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3877,8 +4617,10 @@
       <c r="D107" t="n">
         <v>7.8</v>
       </c>
-      <c r="E107" t="n">
-        <v>3</v>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3888,6 +4630,11 @@
       <c r="G107" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -3910,8 +4657,10 @@
       <c r="D108" t="n">
         <v>1.9</v>
       </c>
-      <c r="E108" t="n">
-        <v>2</v>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
@@ -3919,6 +4668,11 @@
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3939,8 +4693,10 @@
       <c r="D109" t="n">
         <v>1.9</v>
       </c>
-      <c r="E109" t="n">
-        <v>2</v>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
@@ -3948,6 +4704,11 @@
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3968,8 +4729,10 @@
       <c r="D110" t="n">
         <v>1.9</v>
       </c>
-      <c r="E110" t="n">
-        <v>2</v>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
@@ -3977,6 +4740,11 @@
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3997,8 +4765,10 @@
       <c r="D111" t="n">
         <v>8.1</v>
       </c>
-      <c r="E111" t="n">
-        <v>3</v>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -4008,6 +4778,11 @@
       <c r="G111" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:6.1.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.3:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.4:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.5:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.0.6:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:7.1.1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4030,8 +4805,10 @@
       <c r="D112" t="n">
         <v>6.8</v>
       </c>
-      <c r="E112" t="n">
-        <v>2</v>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4041,6 +4818,11 @@
       <c r="G112" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.6:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:itunes:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4063,8 +4845,10 @@
       <c r="D113" t="n">
         <v>6.8</v>
       </c>
-      <c r="E113" t="n">
-        <v>2</v>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -4074,6 +4858,11 @@
       <c r="G113" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:itunes:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.6:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4096,8 +4885,10 @@
       <c r="D114" t="n">
         <v>6.8</v>
       </c>
-      <c r="E114" t="n">
-        <v>2</v>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4107,6 +4898,11 @@
       <c r="G114" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.6:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.2:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:itunes:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4129,8 +4925,10 @@
       <c r="D115" t="n">
         <v>10</v>
       </c>
-      <c r="E115" t="n">
-        <v>2</v>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -4140,6 +4938,11 @@
       <c r="G115" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4162,8 +4965,10 @@
       <c r="D116" t="n">
         <v>6.8</v>
       </c>
-      <c r="E116" t="n">
-        <v>2</v>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4173,6 +4978,11 @@
       <c r="G116" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4195,8 +5005,10 @@
       <c r="D117" t="n">
         <v>6.8</v>
       </c>
-      <c r="E117" t="n">
-        <v>2</v>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -4206,6 +5018,11 @@
       <c r="G117" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4228,8 +5045,10 @@
       <c r="D118" t="n">
         <v>7.5</v>
       </c>
-      <c r="E118" t="n">
-        <v>2</v>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -4239,6 +5058,11 @@
       <c r="G118" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4261,8 +5085,10 @@
       <c r="D119" t="n">
         <v>7.5</v>
       </c>
-      <c r="E119" t="n">
-        <v>2</v>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4272,6 +5098,11 @@
       <c r="G119" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4294,8 +5125,10 @@
       <c r="D120" t="n">
         <v>10</v>
       </c>
-      <c r="E120" t="n">
-        <v>2</v>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
@@ -4303,6 +5136,11 @@
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4323,8 +5161,10 @@
       <c r="D121" t="n">
         <v>10</v>
       </c>
-      <c r="E121" t="n">
-        <v>2</v>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4334,6 +5174,11 @@
       <c r="G121" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4356,8 +5201,10 @@
       <c r="D122" t="n">
         <v>10</v>
       </c>
-      <c r="E122" t="n">
-        <v>2</v>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -4367,6 +5214,11 @@
       <c r="G122" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4389,8 +5241,10 @@
       <c r="D123" t="n">
         <v>10</v>
       </c>
-      <c r="E123" t="n">
-        <v>2</v>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
@@ -4398,6 +5252,11 @@
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4418,8 +5277,10 @@
       <c r="D124" t="n">
         <v>5</v>
       </c>
-      <c r="E124" t="n">
-        <v>2</v>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4429,6 +5290,11 @@
       <c r="G124" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4451,8 +5317,10 @@
       <c r="D125" t="n">
         <v>7.5</v>
       </c>
-      <c r="E125" t="n">
-        <v>2</v>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -4462,6 +5330,11 @@
       <c r="G125" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4484,8 +5357,10 @@
       <c r="D126" t="n">
         <v>10</v>
       </c>
-      <c r="E126" t="n">
-        <v>2</v>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -4495,6 +5370,11 @@
       <c r="G126" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4517,8 +5397,10 @@
       <c r="D127" t="n">
         <v>5</v>
       </c>
-      <c r="E127" t="n">
-        <v>2</v>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -4528,6 +5410,11 @@
       <c r="G127" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4550,8 +5437,10 @@
       <c r="D128" t="n">
         <v>4.3</v>
       </c>
-      <c r="E128" t="n">
-        <v>2</v>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -4561,6 +5450,11 @@
       <c r="G128" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4583,8 +5477,10 @@
       <c r="D129" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E129" t="n">
-        <v>2</v>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -4594,6 +5490,11 @@
       <c r="G129" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4616,8 +5517,10 @@
       <c r="D130" t="n">
         <v>5</v>
       </c>
-      <c r="E130" t="n">
-        <v>2</v>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -4627,6 +5530,11 @@
       <c r="G130" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4649,8 +5557,10 @@
       <c r="D131" t="n">
         <v>6.9</v>
       </c>
-      <c r="E131" t="n">
-        <v>2</v>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -4660,6 +5570,11 @@
       <c r="G131" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4682,8 +5597,10 @@
       <c r="D132" t="n">
         <v>5</v>
       </c>
-      <c r="E132" t="n">
-        <v>2</v>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
@@ -4691,6 +5608,11 @@
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4711,8 +5633,10 @@
       <c r="D133" t="n">
         <v>1.9</v>
       </c>
-      <c r="E133" t="n">
-        <v>2</v>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -4722,6 +5646,11 @@
       <c r="G133" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4744,8 +5673,10 @@
       <c r="D134" t="n">
         <v>7.2</v>
       </c>
-      <c r="E134" t="n">
-        <v>2</v>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
@@ -4753,6 +5684,11 @@
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4773,8 +5709,10 @@
       <c r="D135" t="n">
         <v>1.9</v>
       </c>
-      <c r="E135" t="n">
-        <v>2</v>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4784,6 +5722,11 @@
       <c r="G135" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4806,8 +5749,10 @@
       <c r="D136" t="n">
         <v>1.9</v>
       </c>
-      <c r="E136" t="n">
-        <v>2</v>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -4817,6 +5762,11 @@
       <c r="G136" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4839,8 +5789,10 @@
       <c r="D137" t="n">
         <v>4</v>
       </c>
-      <c r="E137" t="n">
-        <v>2</v>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -4850,6 +5802,11 @@
       <c r="G137" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4872,8 +5829,10 @@
       <c r="D138" t="n">
         <v>5.4</v>
       </c>
-      <c r="E138" t="n">
-        <v>2</v>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -4883,6 +5842,11 @@
       <c r="G138" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4905,8 +5869,10 @@
       <c r="D139" t="n">
         <v>6.9</v>
       </c>
-      <c r="E139" t="n">
-        <v>2</v>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
@@ -4914,6 +5880,11 @@
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4934,8 +5905,10 @@
       <c r="D140" t="n">
         <v>7.1</v>
       </c>
-      <c r="E140" t="n">
-        <v>2</v>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -4945,6 +5918,11 @@
       <c r="G140" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -4967,8 +5945,10 @@
       <c r="D141" t="n">
         <v>7.5</v>
       </c>
-      <c r="E141" t="n">
-        <v>2</v>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -4978,6 +5958,11 @@
       <c r="G141" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -5000,8 +5985,10 @@
       <c r="D142" t="n">
         <v>5</v>
       </c>
-      <c r="E142" t="n">
-        <v>2</v>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -5011,6 +5998,11 @@
       <c r="G142" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -5033,8 +6025,10 @@
       <c r="D143" t="n">
         <v>5</v>
       </c>
-      <c r="E143" t="n">
-        <v>2</v>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -5044,6 +6038,11 @@
       <c r="G143" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -5066,8 +6065,10 @@
       <c r="D144" t="n">
         <v>5</v>
       </c>
-      <c r="E144" t="n">
-        <v>2</v>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -5077,6 +6078,11 @@
       <c r="G144" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -5099,8 +6105,10 @@
       <c r="D145" t="n">
         <v>1.9</v>
       </c>
-      <c r="E145" t="n">
-        <v>2</v>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -5110,6 +6118,11 @@
       <c r="G145" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -5132,8 +6145,10 @@
       <c r="D146" t="n">
         <v>6.9</v>
       </c>
-      <c r="E146" t="n">
-        <v>2</v>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -5143,6 +6158,11 @@
       <c r="G146" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>apple tv</t>
         </is>
       </c>
     </row>
@@ -5165,8 +6185,10 @@
       <c r="D147" t="n">
         <v>5</v>
       </c>
-      <c r="E147" t="n">
-        <v>2</v>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
@@ -5174,6 +6196,11 @@
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:mac_os_x:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5194,8 +6221,10 @@
       <c r="D148" t="n">
         <v>6.8</v>
       </c>
-      <c r="E148" t="n">
-        <v>2</v>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
@@ -5203,6 +6232,11 @@
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.6:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:itunes:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5223,8 +6257,10 @@
       <c r="D149" t="n">
         <v>6.8</v>
       </c>
-      <c r="E149" t="n">
-        <v>2</v>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
@@ -5232,6 +6268,11 @@
           <t>cpe:2.3:a:apple:itunes:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.6:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.4:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5252,8 +6293,10 @@
       <c r="D150" t="n">
         <v>6.8</v>
       </c>
-      <c r="E150" t="n">
-        <v>2</v>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
@@ -5261,6 +6304,11 @@
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:itunes:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.6:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.4:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5281,8 +6329,10 @@
       <c r="D151" t="n">
         <v>6.8</v>
       </c>
-      <c r="E151" t="n">
-        <v>2</v>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
@@ -5290,6 +6340,11 @@
           <t>cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.6:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:itunes:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5310,8 +6365,10 @@
       <c r="D152" t="n">
         <v>6.8</v>
       </c>
-      <c r="E152" t="n">
-        <v>2</v>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
@@ -5319,6 +6376,11 @@
           <t>cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5339,8 +6401,10 @@
       <c r="D153" t="n">
         <v>6.8</v>
       </c>
-      <c r="E153" t="n">
-        <v>2</v>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
@@ -5348,6 +6412,11 @@
           <t>cpe:2.3:a:apple:itunes:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:*:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.5:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.0.6:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:7.1.4:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.0:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.1:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.2:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.3:*:*:*:*:*:*:*|cpe:2.3:a:apple:safari:8.0.4:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>apple tv</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5368,8 +6437,10 @@
       <c r="D154" t="n">
         <v>5.5</v>
       </c>
-      <c r="E154" t="n">
-        <v>3</v>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -5379,6 +6450,11 @@
       <c r="G154" t="inlineStr">
         <is>
           <t>cpe:2.3:a:kodi:kodi:*:*:*:*:*:*:*:*|cpe:2.3:o:debian:debian_linux:7.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>kodi</t>
         </is>
       </c>
     </row>
@@ -5401,8 +6477,10 @@
       <c r="D155" t="n">
         <v>6.3</v>
       </c>
-      <c r="E155" t="n">
-        <v>3</v>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
@@ -5410,6 +6488,11 @@
           <t>cpe:2.3:o:cisco:mx011anm_firmware:mx011an_2.9p6s1_prod_sey:*:*:*:*:*:*:*|cpe:2.3:h:motorola:mx011anm:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>set-top box</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5430,8 +6513,10 @@
       <c r="D156" t="n">
         <v>6.8</v>
       </c>
-      <c r="E156" t="n">
-        <v>3</v>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -5441,6 +6526,11 @@
       <c r="G156" t="inlineStr">
         <is>
           <t>cpe:2.3:o:cisco:mx011anm_firmware:mx011an_2.9p6s1_prod_sey:*:*:*:*:*:*:*|cpe:2.3:h:motorola:mx011anm:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>set-top box</t>
         </is>
       </c>
     </row>
@@ -5463,8 +6553,10 @@
       <c r="D157" t="n">
         <v>7.5</v>
       </c>
-      <c r="E157" t="n">
-        <v>3</v>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -5474,6 +6566,11 @@
       <c r="G157" t="inlineStr">
         <is>
           <t>cpe:2.3:o:cisco:rf_gateway_1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:cisco:rf_gateway_1:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>set-top box</t>
         </is>
       </c>
     </row>
@@ -5496,8 +6593,10 @@
       <c r="D158" t="n">
         <v>6.1</v>
       </c>
-      <c r="E158" t="n">
-        <v>3</v>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -5507,6 +6606,11 @@
       <c r="G158" t="inlineStr">
         <is>
           <t>cpe:2.3:a:kodi:kodi:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>kodi</t>
         </is>
       </c>
     </row>
@@ -5529,8 +6633,10 @@
       <c r="D159" t="n">
         <v>7.5</v>
       </c>
-      <c r="E159" t="n">
-        <v>3</v>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -5540,6 +6646,11 @@
       <c r="G159" t="inlineStr">
         <is>
           <t>cpe:2.3:o:virginmedia:hub_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:virginmedia:hub_3.0:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>virgin media</t>
         </is>
       </c>
     </row>
@@ -5562,8 +6673,10 @@
       <c r="D160" t="n">
         <v>8.1</v>
       </c>
-      <c r="E160" t="n">
-        <v>3</v>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -5573,6 +6686,11 @@
       <c r="G160" t="inlineStr">
         <is>
           <t>cpe:2.3:a:sony:photo_sharing_plus:*:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-50w800c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-50w805c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-50w807c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-50w809c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-50w820c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-55w800c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-55w805c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-65w850c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-65w855c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-65w857c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-75w850c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:kdl-75w855c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:x7500d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-100z9d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-43x800d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-43x800e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-43x830c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-49x700d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-49x800c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-49x800d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-49x800e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-49x830c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-49x835c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-49x835d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-49x837c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-49x839c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-49x900e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55a1e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x700d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x800e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x805c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x806e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x807c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x809c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x810c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x850c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x850d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x855c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x855d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x857c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x857d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x900c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x900e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x905c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x907c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x930d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-55x930e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65a1e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x750d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x800c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x805c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x807c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x809c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x810c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x850c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x850d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x850e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x855c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x855d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x857c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x857d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x900c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x900e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x905c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x907c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x930c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x930d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x930e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x935d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65x937d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-65z9d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x850c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x850d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x850e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x855c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x855d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x857d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x900e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x910c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x940c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x940d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x940e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75x945c:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-75z9d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-77a1e:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-85x850d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-85x855d:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:xbr-85x857d:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>sony bravia</t>
         </is>
       </c>
     </row>
@@ -5595,8 +6713,10 @@
       <c r="D161" t="n">
         <v>7.8</v>
       </c>
-      <c r="E161" t="n">
-        <v>3.1</v>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -5606,6 +6726,11 @@
       <c r="G161" t="inlineStr">
         <is>
           <t>cpe:2.3:a:nvidia:shield_experience:*:*:*:*:*:*:*:*|cpe:2.3:o:google:android:9.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>nvidia shield</t>
         </is>
       </c>
     </row>
@@ -5628,8 +6753,10 @@
       <c r="D162" t="n">
         <v>7.8</v>
       </c>
-      <c r="E162" t="n">
-        <v>3.1</v>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -5639,6 +6766,11 @@
       <c r="G162" t="inlineStr">
         <is>
           <t>cpe:2.3:a:nvidia:shield_experience:*:*:*:*:*:*:*:*|cpe:2.3:o:google:android:9.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>nvidia shield</t>
         </is>
       </c>
     </row>
@@ -5661,8 +6793,10 @@
       <c r="D163" t="n">
         <v>7.5</v>
       </c>
-      <c r="E163" t="n">
-        <v>3.1</v>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -5672,6 +6806,11 @@
       <c r="G163" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sharp:aquos_sh-m02_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_sh-m02:-:*:*:*:*:*:*:*|cpe:2.3:o:sharp:aquos_sh-rm02_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_sh-rm02:-:*:*:*:*:*:*:*|cpe:2.3:o:sharp:aquos_mini_sh-m03_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_mini_sh-m03:-:*:*:*:*:*:*:*|cpe:2.3:o:sharp:aquos_l2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_l2:-:*:*:*:*:*:*:*|cpe:2.3:o:sharp:aquos_sense_lite_sh-m05_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_sense_lite_sh-m05:-:*:*:*:*:*:*:*|cpe:2.3:o:sharp:aquos_sense_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_sense:-:*:*:*:*:*:*:*|cpe:2.3:o:sharp:aquos_compact_sh-m06_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_compact_sh-m06:-:*:*:*:*:*:*:*|cpe:2.3:o:sharp:aquos_sense_plus_sh-m07_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_sense_plus_sh-m07:-:*:*:*:*:*:*:*|cpe:2.3:o:sharp:aquos_sense2_sh-m08_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_sense2_sh-m08:-:*:*:*:*:*:*:*|cpe:2.3:o:sharp:aquos_sense2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sharp:aquos_sense2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>sharp aquos</t>
         </is>
       </c>
     </row>
@@ -5694,8 +6833,10 @@
       <c r="D164" t="n">
         <v>5.9</v>
       </c>
-      <c r="E164" t="n">
-        <v>3.1</v>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -5705,6 +6846,11 @@
       <c r="G164" t="inlineStr">
         <is>
           <t>cpe:2.3:o:thomsonstb:tht741fta_firmware:2.2.1:*:*:*:*:*:*:*|cpe:2.3:h:thomsonstb:tht741fta:-:*:*:*:*:*:*:*|cpe:2.3:o:philips:dtr3502bfta_dvb-t2_firmware:2.2.1:*:*:*:*:*:*:*|cpe:2.3:h:philips:dtr3502bfta_dvb-t2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>set-top box</t>
         </is>
       </c>
     </row>
@@ -5727,8 +6873,10 @@
       <c r="D165" t="n">
         <v>7.8</v>
       </c>
-      <c r="E165" t="n">
-        <v>3.1</v>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
@@ -5736,6 +6884,11 @@
           <t>cpe:2.3:o:thomsonstb:tht741fta_firmware:2.2.1:*:*:*:*:*:*:*|cpe:2.3:h:thomsonstb:tht741fta:-:*:*:*:*:*:*:*|cpe:2.3:o:philips:dtr3502bfta_dvb-t2_firmware:2.2.1:*:*:*:*:*:*:*|cpe:2.3:h:philips:dtr3502bfta_dvb-t2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>set-top box</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5756,8 +6909,10 @@
       <c r="D166" t="n">
         <v>6.6</v>
       </c>
-      <c r="E166" t="n">
-        <v>3.1</v>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -5767,6 +6922,11 @@
       <c r="G166" t="inlineStr">
         <is>
           <t>cpe:2.3:o:netu:wf2429tb_firmware:1.1.10:*:*:*:*:*:*:*|cpe:2.3:h:netu:wf2429tb:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>set-top box</t>
         </is>
       </c>
     </row>
@@ -5789,8 +6949,10 @@
       <c r="D167" t="n">
         <v>6.8</v>
       </c>
-      <c r="E167" t="n">
-        <v>3.1</v>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
@@ -5798,6 +6960,11 @@
           <t>cpe:2.3:a:nvidia:shield_experience:*:*:*:*:*:*:*:*|cpe:2.3:o:google:android:9.0:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>nvidia shield</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5818,8 +6985,10 @@
       <c r="D168" t="n">
         <v>7.8</v>
       </c>
-      <c r="E168" t="n">
-        <v>3.1</v>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -5829,6 +6998,11 @@
       <c r="G168" t="inlineStr">
         <is>
           <t>cpe:2.3:a:nvidia:shield_experience:*:*:*:*:*:*:*:*|cpe:2.3:o:google:android:9.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>nvidia shield</t>
         </is>
       </c>
     </row>
@@ -5851,8 +7025,10 @@
       <c r="D169" t="n">
         <v>6.1</v>
       </c>
-      <c r="E169" t="n">
-        <v>3.1</v>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -5862,6 +7038,11 @@
       <c r="G169" t="inlineStr">
         <is>
           <t>cpe:2.3:a:nvidia:shield_experience:*:*:*:*:*:*:*:*|cpe:2.3:o:google:android:9.0:*:*:*:*:*:*:*|cpe:2.3:o:nvidia:linux_for_tegra:*:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:jetson_agx_xavier:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:jetson_nano:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:jetson_nano_2gb:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:jetson_tx1:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:jetson_tx2:-:*:*:*:*:*:*:*|cpe:2.3:h:nvidia:jetson_xavier_nx:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>nvidia shield</t>
         </is>
       </c>
     </row>
@@ -5884,8 +7065,10 @@
       <c r="D170" t="n">
         <v>5</v>
       </c>
-      <c r="E170" t="n">
-        <v>3.1</v>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -5895,6 +7078,11 @@
       <c r="G170" t="inlineStr">
         <is>
           <t>cpe:2.3:a:openhab:openhab:*:*:*:*:*:*:*:*|cpe:2.3:a:openhab:openhab:3.0.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>roku</t>
         </is>
       </c>
     </row>
@@ -5917,8 +7105,10 @@
       <c r="D171" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E171" t="n">
-        <v>3.1</v>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
@@ -5926,6 +7116,11 @@
           <t>cpe:2.3:o:google:android:8.1:*:*:*:*:*:*:*|cpe:2.3:o:google:android:9.0:*:*:*:*:*:*:*|cpe:2.3:o:google:android:10.0:*:*:*:*:*:*:*|cpe:2.3:o:google:android:11.0:*:*:*:*:*:*:*|cpe:2.3:o:google:android:12.0:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>android tv</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5946,8 +7141,10 @@
       <c r="D172" t="n">
         <v>7.5</v>
       </c>
-      <c r="E172" t="n">
-        <v>3.1</v>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -5957,6 +7154,11 @@
       <c r="G172" t="inlineStr">
         <is>
           <t>cpe:2.3:a:allwinnertech:android_q_sdk:1.0:*:*:*:*:*:*:*|cpe:2.3:h:allwinnertech:r818:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>allwinner</t>
         </is>
       </c>
     </row>
@@ -5979,8 +7181,10 @@
       <c r="D173" t="n">
         <v>7.5</v>
       </c>
-      <c r="E173" t="n">
-        <v>3.1</v>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -5990,6 +7194,11 @@
       <c r="G173" t="inlineStr">
         <is>
           <t>cpe:2.3:a:allwinnertech:android_q_sdk:1.0:*:*:*:*:*:*:*|cpe:2.3:h:allwinnertech:r818:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>allwinner</t>
         </is>
       </c>
     </row>
@@ -6012,8 +7221,10 @@
       <c r="D174" t="n">
         <v>7.5</v>
       </c>
-      <c r="E174" t="n">
-        <v>3.1</v>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -6023,6 +7234,11 @@
       <c r="G174" t="inlineStr">
         <is>
           <t>cpe:2.3:a:allwinnertech:android_q_sdk:1.0:*:*:*:*:*:*:*|cpe:2.3:h:allwinnertech:r818:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>allwinner</t>
         </is>
       </c>
     </row>
@@ -6045,8 +7261,10 @@
       <c r="D175" t="n">
         <v>7.5</v>
       </c>
-      <c r="E175" t="n">
-        <v>3.1</v>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -6056,6 +7274,11 @@
       <c r="G175" t="inlineStr">
         <is>
           <t>cpe:2.3:a:allwinnertech:android_q_sdk:1.0:*:*:*:*:*:*:*|cpe:2.3:h:allwinnertech:r818:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>allwinner</t>
         </is>
       </c>
     </row>
@@ -6078,8 +7301,10 @@
       <c r="D176" t="n">
         <v>7.5</v>
       </c>
-      <c r="E176" t="n">
-        <v>3.1</v>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -6089,6 +7314,11 @@
       <c r="G176" t="inlineStr">
         <is>
           <t>cpe:2.3:a:allwinnertech:android_q_sdk:1.0:*:*:*:*:*:*:*|cpe:2.3:h:allwinnertech:r818:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>allwinner</t>
         </is>
       </c>
     </row>
@@ -6111,8 +7341,10 @@
       <c r="D177" t="n">
         <v>7.5</v>
       </c>
-      <c r="E177" t="n">
-        <v>3.1</v>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
@@ -6120,6 +7352,11 @@
           <t>cpe:2.3:a:allwinnertech:android_q_sdk:1.0:*:*:*:*:*:*:*|cpe:2.3:h:allwinnertech:r818:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>allwinner</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6140,8 +7377,10 @@
       <c r="D178" t="n">
         <v>7.5</v>
       </c>
-      <c r="E178" t="n">
-        <v>3.1</v>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -6151,6 +7390,11 @@
       <c r="G178" t="inlineStr">
         <is>
           <t>cpe:2.3:a:allwinnertech:android_q_sdk:1.0:*:*:*:*:*:*:*|cpe:2.3:h:allwinnertech:r818:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>allwinner</t>
         </is>
       </c>
     </row>
@@ -6176,8 +7420,10 @@
       <c r="D179" t="n">
         <v>4.3</v>
       </c>
-      <c r="E179" t="n">
-        <v>3.1</v>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -6187,6 +7433,11 @@
       <c r="G179" t="inlineStr">
         <is>
           <t>cpe:2.3:o:amazon:fire_os:*:*:*:*:*:*:*:*|cpe:2.3:h:amazon:fire_tv_stick_3rd_gen:-:*:*:*:*:*:*:*|cpe:2.3:h:bestbuy:insignia_tv:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>amazon fire tv|insignia tv</t>
         </is>
       </c>
     </row>
@@ -6212,8 +7463,10 @@
       <c r="D180" t="n">
         <v>6.1</v>
       </c>
-      <c r="E180" t="n">
-        <v>3.1</v>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -6223,6 +7476,11 @@
       <c r="G180" t="inlineStr">
         <is>
           <t>cpe:2.3:o:amazon:fire_os:*:*:*:*:*:*:*:*|cpe:2.3:h:amazon:fire_tv_stick_3rd_gen:-:*:*:*:*:*:*:*|cpe:2.3:h:bestbuy:insignia_tv:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>amazon fire tv|insignia tv</t>
         </is>
       </c>
     </row>
@@ -6248,8 +7506,10 @@
       <c r="D181" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E181" t="n">
-        <v>3.1</v>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -6259,6 +7519,11 @@
       <c r="G181" t="inlineStr">
         <is>
           <t>cpe:2.3:o:amazon:fire_os:*:*:*:*:*:*:*:*|cpe:2.3:h:amazon:fire_tv_stick_3rd_gen:-:*:*:*:*:*:*:*|cpe:2.3:h:bestbuy:insignia_tv:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>amazon fire tv|insignia tv</t>
         </is>
       </c>
     </row>
@@ -6281,8 +7546,10 @@
       <c r="D182" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E182" t="n">
-        <v>3.1</v>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -6292,6 +7559,11 @@
       <c r="G182" t="inlineStr">
         <is>
           <t>cpe:2.3:o:microsoft:windows_10_1507:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10_1607:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10_1809:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10_21h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10_22h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_21h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_22h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_server_2016:-:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_server_2019:-:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_server_2022:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>miracast</t>
         </is>
       </c>
     </row>
@@ -6314,8 +7586,10 @@
       <c r="D183" t="n">
         <v>5.5</v>
       </c>
-      <c r="E183" t="n">
-        <v>3.1</v>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -6325,6 +7599,11 @@
       <c r="G183" t="inlineStr">
         <is>
           <t>cpe:2.3:a:kodi:kodi:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>kodi</t>
         </is>
       </c>
     </row>
@@ -6379,8 +7658,10 @@
       <c r="D184" t="n">
         <v>5.5</v>
       </c>
-      <c r="E184" t="n">
-        <v>3.1</v>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
@@ -6388,6 +7669,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>amlogic</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6408,8 +7694,10 @@
       <c r="D185" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E185" t="n">
-        <v>3.1</v>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -6419,6 +7707,11 @@
       <c r="G185" t="inlineStr">
         <is>
           <t>cpe:2.3:o:wyze:cam_v3_firmware:4.36.11.5859:*:*:*:*:*:*:*|cpe:2.3:h:wyze:cam_v3:-:*:*:*:*:*:*:*|cpe:2.3:o:roku:indoor_camera_se_firmware:3.0.2.4679:*:*:*:*:*:*:*|cpe:2.3:h:roku:indoor_camera_se:-:*:*:*:*:*:*:*|cpe:2.3:a:throughtek:kalay_platform:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>roku</t>
         </is>
       </c>
     </row>
@@ -6441,8 +7734,10 @@
       <c r="D186" t="n">
         <v>6.5</v>
       </c>
-      <c r="E186" t="n">
-        <v>3.1</v>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -6452,6 +7747,11 @@
       <c r="G186" t="inlineStr">
         <is>
           <t>cpe:2.3:o:wyze:cam_v3_firmware:4.36.11.5859:*:*:*:*:*:*:*|cpe:2.3:h:wyze:cam_v3:-:*:*:*:*:*:*:*|cpe:2.3:o:roku:indoor_camera_se_firmware:3.0.2.4679:*:*:*:*:*:*:*|cpe:2.3:h:roku:indoor_camera_se:-:*:*:*:*:*:*:*|cpe:2.3:o:owletcare:cam_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:owletcare:cam:-:*:*:*:*:*:*:*|cpe:2.3:o:owletcare:cam_2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:owletcare:cam_2:-:*:*:*:*:*:*:*|cpe:2.3:a:throughtek:kalay_platform:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>roku</t>
         </is>
       </c>
     </row>
@@ -6474,8 +7774,10 @@
       <c r="D187" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E187" t="n">
-        <v>3.1</v>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -6485,6 +7787,11 @@
       <c r="G187" t="inlineStr">
         <is>
           <t>cpe:2.3:o:wyze:cam_v3_firmware:4.36.11.5859:*:*:*:*:*:*:*|cpe:2.3:h:wyze:cam_v3:-:*:*:*:*:*:*:*|cpe:2.3:o:roku:indoor_camera_se_firmware:3.0.2.4679:*:*:*:*:*:*:*|cpe:2.3:h:roku:indoor_camera_se:-:*:*:*:*:*:*:*|cpe:2.3:o:owletcare:cam_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:owletcare:cam:-:*:*:*:*:*:*:*|cpe:2.3:o:owletcare:cam_2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:owletcare:cam_2:-:*:*:*:*:*:*:*|cpe:2.3:a:throughtek:kalay_platform:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>roku</t>
         </is>
       </c>
     </row>
@@ -6560,8 +7867,10 @@
       <c r="D188" t="n">
         <v>7.8</v>
       </c>
-      <c r="E188" t="n">
-        <v>3.1</v>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -6571,6 +7880,11 @@
       <c r="G188" t="inlineStr">
         <is>
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>kodi</t>
         </is>
       </c>
     </row>
@@ -6596,13 +7910,20 @@
       <c r="D189" t="n">
         <v>5.5</v>
       </c>
-      <c r="E189" t="n">
-        <v>3.1</v>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>amlogic</t>
         </is>
       </c>
     </row>
@@ -6667,8 +7988,10 @@
       <c r="D190" t="n">
         <v>7.8</v>
       </c>
-      <c r="E190" t="n">
-        <v>3.1</v>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
@@ -6676,6 +7999,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>amlogic</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6696,8 +8024,10 @@
       <c r="D191" t="n">
         <v>4.7</v>
       </c>
-      <c r="E191" t="n">
-        <v>3.1</v>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -6707,6 +8037,11 @@
       <c r="G191" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tcl:65c655_firmware:v8-r75pt01-lf1v269.001116:*:*:*:*:*:*:*|cpe:2.3:h:tcl:65c655:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>android tv</t>
         </is>
       </c>
     </row>
@@ -6729,8 +8064,10 @@
       <c r="D192" t="n">
         <v>7.5</v>
       </c>
-      <c r="E192" t="n">
-        <v>3.1</v>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -6740,6 +8077,11 @@
       <c r="G192" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tcl:65c655_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:tcl:65c655:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>dlna</t>
         </is>
       </c>
     </row>
@@ -6771,6 +8113,11 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>amlogic</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6791,8 +8138,10 @@
       <c r="D194" t="n">
         <v>7.5</v>
       </c>
-      <c r="E194" t="n">
-        <v>3.1</v>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -6802,6 +8151,11 @@
       <c r="G194" t="inlineStr">
         <is>
           <t>cpe:2.3:a:sony:bravia_signage:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>sony bravia</t>
         </is>
       </c>
     </row>
@@ -6824,8 +8178,10 @@
       <c r="D195" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E195" t="n">
-        <v>3.1</v>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -6835,6 +8191,11 @@
       <c r="G195" t="inlineStr">
         <is>
           <t>cpe:2.3:a:sony:bravia_signage:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>sony bravia</t>
         </is>
       </c>
     </row>
@@ -6857,8 +8218,10 @@
       <c r="D196" t="n">
         <v>6.1</v>
       </c>
-      <c r="E196" t="n">
-        <v>3.1</v>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -6868,6 +8231,11 @@
       <c r="G196" t="inlineStr">
         <is>
           <t>cpe:2.3:a:sony:bravia_signage:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>sony bravia</t>
         </is>
       </c>
     </row>
@@ -6890,8 +8258,10 @@
       <c r="D197" t="n">
         <v>6.1</v>
       </c>
-      <c r="E197" t="n">
-        <v>3.1</v>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -6899,6 +8269,11 @@
         </is>
       </c>
       <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>dlna</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6927,8 +8302,10 @@
       <c r="D198" t="n">
         <v>5.5</v>
       </c>
-      <c r="E198" t="n">
-        <v>3.1</v>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -6938,6 +8315,11 @@
       <c r="G198" t="inlineStr">
         <is>
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.17:-:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc3:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc4:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc5:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc6:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc7:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>amlogic</t>
         </is>
       </c>
     </row>
@@ -6966,13 +8348,20 @@
       <c r="D199" t="n">
         <v>5.5</v>
       </c>
-      <c r="E199" t="n">
-        <v>3.1</v>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.18:-:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc3:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc4:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc5:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc6:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>amlogic</t>
         </is>
       </c>
     </row>
@@ -7005,13 +8394,20 @@
       <c r="D200" t="n">
         <v>7.8</v>
       </c>
-      <c r="E200" t="n">
-        <v>3.1</v>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc3:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>amlogic</t>
         </is>
       </c>
     </row>
